--- a/output/full_scan/batch_seq7_2026-09-17.xlsx
+++ b/output/full_scan/batch_seq7_2026-09-17.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -633,21 +633,21 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6491</v>
+        <v>6538</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>855.2487472081978</v>
+        <v>879.5259699824986</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>401</v>
+        <v>353</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>64.47743576637359</v>
+        <v>71.75190379959741</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>24.32969675732712</v>
+        <v>60.88242996118284</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.391978934798579</v>
+        <v>0.368988210694375</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.7348043244728686</v>
+        <v>6.279661089439209</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6530</v>
+        <v>6491</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>840.5670877144518</v>
+        <v>855.2487472081978</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>99.7</v>
+        <v>401</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>60.60161768787828</v>
+        <v>64.47743576637359</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>28.73033110039633</v>
+        <v>24.32969675732712</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.972617085339416</v>
+        <v>1.391978934798579</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.099078153317194</v>
+        <v>0.7348043244728686</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6668</v>
+        <v>6530</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>798.3354449829228</v>
+        <v>840.5670877144518</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>44.8</v>
+        <v>99.7</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>63.66564980534541</v>
+        <v>60.60161768787828</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>38.04423945913616</v>
+        <v>28.73033110039633</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.133544498292283</v>
+        <v>1.972617085339416</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.112327710834625</v>
+        <v>-0.099078153317194</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6708</v>
+        <v>6668</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>771.6521100084353</v>
+        <v>798.3354449829228</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>39.15</v>
+        <v>44.8</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>53.05255272760494</v>
+        <v>63.66564980534541</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>6.084350706484655</v>
+        <v>38.04423945913616</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>5.114526977007226</v>
+        <v>1.133544498292283</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.187553879936511</v>
+        <v>0.112327710834625</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6532</v>
+        <v>6708</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>764.223519250818</v>
+        <v>771.6521100084353</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>93.90000000000001</v>
+        <v>39.15</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>55.37946718089807</v>
+        <v>53.05255272760494</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>37.34580553835049</v>
+        <v>6.084350706484655</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.8932313229020283</v>
+        <v>5.114526977007226</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-1.023831970071587</v>
+        <v>-0.187553879936511</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6672</v>
+        <v>6532</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>731.1890559187174</v>
+        <v>764.223519250818</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>293.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>56.00487767084766</v>
+        <v>55.37946718089807</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>22.39378121664364</v>
+        <v>37.34580553835049</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.060705592422977</v>
+        <v>0.8932313229020283</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-0.2133207795010729</v>
+        <v>-1.023831970071587</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6505</v>
+        <v>6672</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>686.2978740915913</v>
+        <v>731.1890559187174</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>86.2</v>
+        <v>293.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>63.62723512905096</v>
+        <v>56.00487767084766</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>40.16144511256366</v>
+        <v>22.39378121664364</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.374400018782213</v>
+        <v>2.060705592422977</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.4055183133025206</v>
+        <v>-0.2133207795010729</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6640</v>
+        <v>6505</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>682.1977274416752</v>
+        <v>686.2978740915913</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1120</v>
+        <v>86.2</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>51.29847228276547</v>
+        <v>63.62723512905096</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>26.45942035862215</v>
+        <v>40.16144511256366</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.568163164302025</v>
+        <v>1.374400018782213</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-13.02718437213436</v>
+        <v>0.4055183133025206</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6742</v>
+        <v>6640</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>663.6365070633078</v>
+        <v>682.1977274416752</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>51.2</v>
+        <v>1120</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>66.59368857412505</v>
+        <v>51.29847228276547</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>27.66409216429395</v>
+        <v>26.45942035862215</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3.422953602654174</v>
+        <v>0.568163164302025</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.6487643265856384</v>
+        <v>-13.02718437213436</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6743</v>
+        <v>6742</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>624.959485562792</v>
+        <v>663.6365070633078</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>29.3</v>
+        <v>51.2</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>60.95973171780764</v>
+        <v>66.59368857412505</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>22.61620523671036</v>
+        <v>27.66409216429395</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.13280351383925</v>
+        <v>3.422953602654174</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.1755668447973857</v>
+        <v>0.6487643265856384</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6805</v>
+        <v>6743</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>623.4876378070198</v>
+        <v>624.959485562792</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2090</v>
+        <v>29.3</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>53.0263651014949</v>
+        <v>60.95973171780764</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>25.47596562883598</v>
+        <v>22.61620523671036</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.6993346666308876</v>
+        <v>1.13280351383925</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-34.61884093417014</v>
+        <v>0.1755668447973857</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6716</v>
+        <v>6805</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>614.6796337767854</v>
+        <v>623.4876378070198</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>117</v>
+        <v>2090</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>49.87520121588054</v>
+        <v>53.0263651014949</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>27.81846626635873</v>
+        <v>25.47596562883598</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.6186254960439953</v>
+        <v>0.6993346666308876</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-1.923793966055908</v>
+        <v>-34.61884093417014</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6655</v>
+        <v>6716</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>614.2431964634475</v>
+        <v>614.6796337767854</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>124.5</v>
+        <v>117</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>53.71975013127562</v>
+        <v>49.87520121588054</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>10.95973575078303</v>
+        <v>27.81846626635873</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.524319646344744</v>
+        <v>0.6186254960439953</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>2.348189262530187</v>
+        <v>-1.923793966055908</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6589</v>
+        <v>6655</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>593.0799139844455</v>
+        <v>614.2431964634475</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>51.2</v>
+        <v>124.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>59.93070850779418</v>
+        <v>53.71975013127562</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>14.97994817914256</v>
+        <v>10.95973575078303</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2.646941605144646</v>
+        <v>1.524319646344744</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.1584632640872912</v>
+        <v>2.348189262530187</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6670</v>
+        <v>6589</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>591.3594633344187</v>
+        <v>593.0799139844455</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>273.5</v>
+        <v>51.2</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>52.02076939197424</v>
+        <v>59.93070850779418</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>27.83395876729113</v>
+        <v>14.97994817914256</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.5523126856714984</v>
+        <v>2.646941605144646</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.9200003503762963</v>
+        <v>0.1584632640872912</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6667</v>
+        <v>6670</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>574.9461107954194</v>
+        <v>591.3594633344187</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>238.5</v>
+        <v>273.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>52.97765693202219</v>
+        <v>52.02076939197424</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>32.61206291966344</v>
+        <v>27.83395876729113</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.4474106829063027</v>
+        <v>0.5523126856714984</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.9738042429050572</v>
+        <v>-0.9200003503762963</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6782</v>
+        <v>6667</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>570.2184475456129</v>
+        <v>574.9461107954194</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>249</v>
+        <v>238.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>65.7190654416423</v>
+        <v>52.97765693202219</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>22.76991086828495</v>
+        <v>32.61206291966344</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.239422071026343</v>
+        <v>0.4474106829063027</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.6625688215565351</v>
+        <v>0.9738042429050572</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6548</v>
+        <v>6782</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>557.177942677948</v>
+        <v>570.2184475456129</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>72.59999999999999</v>
+        <v>249</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>50.69803654045735</v>
+        <v>65.7190654416423</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>10.28471732267576</v>
+        <v>22.76991086828495</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.245695452585348</v>
+        <v>1.239422071026343</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.0436021320905765</v>
+        <v>-0.6625688215565351</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6654</v>
+        <v>6548</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>547.3181896685271</v>
+        <v>557.177942677948</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>200</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>54.44584292304686</v>
+        <v>50.69803654045735</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>25.32179123608424</v>
+        <v>10.28471732267576</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.1466461204049933</v>
+        <v>1.245695452585348</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.9513878231118564</v>
+        <v>0.0436021320905765</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6715</v>
+        <v>6654</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>543.414651946494</v>
+        <v>547.3181896685271</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>394</v>
+        <v>200</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>56.10868220937755</v>
+        <v>54.44584292304686</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>12.42648964066758</v>
+        <v>25.32179123608424</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>3.641465194649402</v>
+        <v>0.1466461204049933</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>7.169354250954921</v>
+        <v>-0.9513878231118564</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6771</v>
+        <v>6715</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>531.792579499226</v>
+        <v>543.414651946494</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>42.4</v>
+        <v>394</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>63.08939921835798</v>
+        <v>56.10868220937755</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>24.49843706701721</v>
+        <v>12.42648964066758</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.477163618596354</v>
+        <v>3.641465194649402</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,48 +1736,48 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.0539329735029275</v>
+        <v>7.169354250954921</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6806</v>
+        <v>6771</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>528.7768356926886</v>
+        <v>531.792579499226</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>3.51</v>
+        <v>42.4</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G25" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>31.6950277170751</v>
+        <v>63.08939921835798</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>32.59322795348182</v>
+        <v>24.49843706701721</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>1.477163618596354</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,48 +1789,48 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.4112821206575292</v>
+        <v>-0.0539329735029275</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6691</v>
+        <v>6806</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>528.4463518388549</v>
+        <v>528.7768356926886</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>610</v>
+        <v>3.51</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G26" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>41.33810341505159</v>
+        <v>31.6950277170751</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>20.01237266089297</v>
+        <v>32.59322795348182</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.8530909277571515</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>2.347570647685313</v>
+        <v>0.4112821206575292</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6830</v>
+        <v>6691</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>522.8947706063691</v>
+        <v>528.4463518388549</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>512</v>
+        <v>610</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>48.5685867494819</v>
+        <v>41.33810341505159</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>31.63998941994046</v>
+        <v>20.01237266089297</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.5744830079924808</v>
+        <v>0.8530909277571515</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-9.725075879433859</v>
+        <v>2.347570647685313</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6613</v>
+        <v>6830</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>516.1737332271309</v>
+        <v>522.8947706063691</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>261</v>
+        <v>512</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>46.45845917005455</v>
+        <v>48.5685867494819</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>8.192582680629657</v>
+        <v>31.63998941994046</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.4332917859417431</v>
+        <v>0.5744830079924808</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1.273422746794229</v>
+        <v>-9.725075879433859</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6643</v>
+        <v>6613</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>511.0570145680866</v>
+        <v>516.1737332271309</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>438</v>
+        <v>261</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>54.64405717897132</v>
+        <v>46.45845917005455</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>12.56920021752816</v>
+        <v>8.192582680629657</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.99238163592017</v>
+        <v>0.4332917859417431</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>1.753222473506957</v>
+        <v>1.273422746794229</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6510</v>
+        <v>6643</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>506.4953535536943</v>
+        <v>511.0570145680866</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>3200</v>
+        <v>438</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>52.02536366184554</v>
+        <v>54.64405717897132</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>32.29336689112084</v>
+        <v>12.56920021752816</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.716954611305693</v>
+        <v>1.99238163592017</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-16.94322303991339</v>
+        <v>1.753222473506957</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6568</v>
+        <v>6510</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>486.0502389742212</v>
+        <v>506.4953535536943</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>139</v>
+        <v>3200</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>54.73833128295706</v>
+        <v>52.02536366184554</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>20.66086929489355</v>
+        <v>32.29336689112084</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2.110345293488668</v>
+        <v>0.716954611305693</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.9405283050862934</v>
+        <v>-16.94322303991339</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6579</v>
+        <v>6568</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>485.1297824803473</v>
+        <v>486.0502389742212</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>51.37969996625682</v>
+        <v>54.73833128295706</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>21.16331632940347</v>
+        <v>20.66086929489355</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.9642930408632676</v>
+        <v>2.110345293488668</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.81334692495511</v>
+        <v>0.9405283050862934</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6666</v>
+        <v>6579</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>477.0989533969892</v>
+        <v>485.1297824803473</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>44.75</v>
+        <v>152</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>56.32531131532009</v>
+        <v>51.37969996625682</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>11.48645128273113</v>
+        <v>21.16331632940347</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.4913090408307589</v>
+        <v>0.9642930408632676</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.0190702979383345</v>
+        <v>0.81334692495511</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6657</v>
+        <v>6666</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>476.2181078139324</v>
+        <v>477.0989533969892</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>34.3</v>
+        <v>44.75</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>57.75126949128502</v>
+        <v>56.32531131532009</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>26.10700181688209</v>
+        <v>11.48645128273113</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.5439857553590565</v>
+        <v>0.4913090408307589</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.3472157356024467</v>
+        <v>-0.0190702979383345</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6651</v>
+        <v>6657</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>471.1254913657221</v>
+        <v>476.2181078139324</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>147</v>
+        <v>34.3</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>55.62875479852162</v>
+        <v>57.75126949128502</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>21.75591779675942</v>
+        <v>26.10700181688209</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.6939008170245108</v>
+        <v>0.5439857553590565</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.7268068852235654</v>
+        <v>0.3472157356024467</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6706</v>
+        <v>6651</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>467.9929953031208</v>
+        <v>471.1254913657221</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>63.75245505932007</v>
+        <v>55.62875479852162</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>31.5900160484498</v>
+        <v>21.75591779675942</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>2.531299767976802</v>
+        <v>0.6939008170245108</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>2.59307943280642</v>
+        <v>-0.7268068852235654</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6486</v>
+        <v>6706</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>466.8491466762573</v>
+        <v>467.9929953031208</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>81.2</v>
+        <v>145</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>59.87120573295835</v>
+        <v>63.75245505932007</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>43.7040802193901</v>
+        <v>31.5900160484498</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.341356951036997</v>
+        <v>2.531299767976802</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.0385364161267174</v>
+        <v>2.59307943280642</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6834</v>
+        <v>6486</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>448.4578342430722</v>
+        <v>466.8491466762573</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>101.5</v>
+        <v>81.2</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>54.92185012495626</v>
+        <v>59.87120573295835</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>19.97167354444466</v>
+        <v>43.7040802193901</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.329987826134565</v>
+        <v>0.341356951036997</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.7660994412705621</v>
+        <v>0.0385364161267174</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6727</v>
+        <v>6834</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>亞泰金屬</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>435.7045392782972</v>
+        <v>448.4578342430722</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>470.5</v>
+        <v>101.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>46.83727177291041</v>
+        <v>54.92185012495626</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>21.68896522402288</v>
+        <v>19.97167354444466</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.9381379118718476</v>
+        <v>1.329987826134565</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-11.49931749380474</v>
+        <v>0.7660994412705621</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6693</v>
+        <v>6727</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>434.6582495075365</v>
+        <v>435.7045392782972</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>180.5</v>
+        <v>470.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>51.43575076589266</v>
+        <v>46.83727177291041</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>14.72684803306588</v>
+        <v>21.68896522402288</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.056131843648372</v>
+        <v>0.9381379118718476</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.6686976425728695</v>
+        <v>-11.49931749380474</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6570</v>
+        <v>6693</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>429.3680061397502</v>
+        <v>434.6582495075365</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>46.7</v>
+        <v>180.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>33.09339381847506</v>
+        <v>51.43575076589266</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>26.37083805502848</v>
+        <v>14.72684803306588</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.8696657068091836</v>
+        <v>1.056131843648372</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.4289848343054792</v>
+        <v>0.6686976425728695</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6689</v>
+        <v>6570</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>427.6470176189801</v>
+        <v>429.3680061397502</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>65.5</v>
+        <v>46.7</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>55.52989160892218</v>
+        <v>33.09339381847506</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>20.2970323391376</v>
+        <v>26.37083805502848</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.164701761898008</v>
+        <v>0.8696657068091836</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.6445232939770983</v>
+        <v>-0.4289848343054792</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6533</v>
+        <v>6689</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>421.5166667223837</v>
+        <v>427.6470176189801</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>251.5</v>
+        <v>65.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>53.95114557833934</v>
+        <v>55.52989160892218</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>17.60921293322498</v>
+        <v>20.2970323391376</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.473152821602872</v>
+        <v>1.164701761898008</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-3.574868908081683</v>
+        <v>0.6445232939770983</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6598</v>
+        <v>6533</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>419.2137649690469</v>
+        <v>421.5166667223837</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>27.9</v>
+        <v>251.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>49.81495048118582</v>
+        <v>53.95114557833934</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>16.88413052159837</v>
+        <v>17.60921293322498</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.380256312789978</v>
+        <v>1.473152821602872</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.0765845149632511</v>
+        <v>-3.574868908081683</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6515</v>
+        <v>6598</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>411.8760964283938</v>
+        <v>419.2137649690469</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>6120</v>
+        <v>27.9</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>39.8630164079471</v>
+        <v>49.81495048118582</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>15.77396908991841</v>
+        <v>16.88413052159837</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.8899619161306197</v>
+        <v>0.380256312789978</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-74.94935987818126</v>
+        <v>-0.0765845149632511</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6790</v>
+        <v>6515</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>408.7372455147036</v>
+        <v>411.8760964283938</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>38</v>
+        <v>6120</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>47.75545609087537</v>
+        <v>39.8630164079471</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>10.97942275521158</v>
+        <v>15.77396908991841</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.8137415750157112</v>
+        <v>0.8899619161306197</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.0137362994838327</v>
+        <v>-74.94935987818126</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, williams_r_recovery</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6560</v>
+        <v>6790</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>398.5984183118817</v>
+        <v>408.7372455147036</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>34.25</v>
+        <v>38</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>56.32412313362994</v>
+        <v>47.75545609087537</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>11.40667840215971</v>
+        <v>10.97942275521158</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>5.551775829435937</v>
+        <v>0.8137415750157112</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.6077996711625029</v>
+        <v>0.0137362994838327</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6770</v>
+        <v>6560</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>397.8081664715738</v>
+        <v>398.5984183118817</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>71.2</v>
+        <v>34.25</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>52.47500159147959</v>
+        <v>56.32412313362994</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>9.206222032704821</v>
+        <v>11.40667840215971</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.8750454051616077</v>
+        <v>5.551775829435937</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.2402279256450065</v>
+        <v>0.6077996711625029</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6597</v>
+        <v>6770</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>388.9904980694601</v>
+        <v>397.8081664715738</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>69.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>52.68397684757181</v>
+        <v>52.47500159147959</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>7.702756590529432</v>
+        <v>9.206222032704821</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>2.402260848691173</v>
+        <v>0.8750454051616077</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.5748957710632356</v>
+        <v>-0.2402279256450065</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6684</v>
+        <v>6597</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>386.5919469396644</v>
+        <v>388.9904980694601</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>47.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>54.47633610796385</v>
+        <v>52.68397684757181</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>10.27521808307564</v>
+        <v>7.702756590529432</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>4.121888847779886</v>
+        <v>2.402260848691173</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.2233254371453767</v>
+        <v>0.5748957710632356</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6683</v>
+        <v>6684</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>385.1414271407598</v>
+        <v>386.5919469396644</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>1575</v>
+        <v>47.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,49 +3149,49 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>64.55879012576318</v>
+        <v>54.47633610796385</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>16.22719988381877</v>
+        <v>10.27521808307564</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>2.129924380880817</v>
+        <v>4.121888847779886</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>29.0932936799759</v>
+        <v>0.2233254371453767</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6582</v>
+        <v>6683</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>382.5717400901615</v>
+        <v>385.1414271407598</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>31.3</v>
+        <v>1575</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,49 +3202,49 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>40.76876553985399</v>
+        <v>64.55879012576318</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>20.3899101972918</v>
+        <v>16.22719988381877</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>2.68060921165429</v>
+        <v>2.129924380880817</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.102761993303593</v>
+        <v>29.0932936799759</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6581</v>
+        <v>6582</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>382.0800577679265</v>
+        <v>382.5717400901615</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>109.5</v>
+        <v>31.3</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>51.3735208695355</v>
+        <v>40.76876553985399</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>22.32064604103689</v>
+        <v>20.3899101972918</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.2592450822972644</v>
+        <v>2.68060921165429</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.0605810210824072</v>
+        <v>-0.102761993303593</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6741</v>
+        <v>6581</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>379.2841280696175</v>
+        <v>382.0800577679265</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>59.1</v>
+        <v>109.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>54.25798361788559</v>
+        <v>51.3735208695355</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>22.31197348402064</v>
+        <v>22.32064604103689</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.2947268157734791</v>
+        <v>0.2592450822972644</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.1162001029700683</v>
+        <v>-0.0605810210824072</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6504</v>
+        <v>6741</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>365.7394615981784</v>
+        <v>379.2841280696175</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>36.95</v>
+        <v>59.1</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>45.35687026824175</v>
+        <v>54.25798361788559</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>20.59829124503313</v>
+        <v>22.31197348402064</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.5065548578041701</v>
+        <v>0.2947268157734791</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.0813494142260648</v>
+        <v>-0.1162001029700683</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6664</v>
+        <v>6504</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>364.8167516855903</v>
+        <v>365.7394615981784</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>332</v>
+        <v>36.95</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>40.67493116196813</v>
+        <v>45.35687026824175</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>11.21852517228204</v>
+        <v>20.59829124503313</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.517517964381663</v>
+        <v>0.5065548578041701</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-2.388166254114223</v>
+        <v>-0.0813494142260648</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6768</v>
+        <v>6664</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>363.8907232755768</v>
+        <v>364.8167516855903</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>62.5</v>
+        <v>332</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>36.90508074590861</v>
+        <v>40.67493116196813</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>28.9300166558536</v>
+        <v>11.21852517228204</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.8089241719134957</v>
+        <v>0.517517964381663</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.0748627694812387</v>
+        <v>-2.388166254114223</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6584</v>
+        <v>6768</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>362.8632874761481</v>
+        <v>363.8907232755768</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>551</v>
+        <v>62.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>43.25333333296103</v>
+        <v>36.90508074590861</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>21.77735674622966</v>
+        <v>28.9300166558536</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3147989306417468</v>
+        <v>0.8089241719134957</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-10.20975875075558</v>
+        <v>0.0748627694812387</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6690</v>
+        <v>6584</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>357.1252600284076</v>
+        <v>362.8632874761481</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>178</v>
+        <v>551</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>62.24503992838719</v>
+        <v>43.25333333296103</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>23.86444478347336</v>
+        <v>21.77735674622966</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.312526002840756</v>
+        <v>0.3147989306417468</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>2.052690988738493</v>
+        <v>-10.20975875075558</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6799</v>
+        <v>6690</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>355.6904821360484</v>
+        <v>357.1252600284076</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>81.2</v>
+        <v>178</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>51.09173789719254</v>
+        <v>62.24503992838719</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>11.33819739891984</v>
+        <v>23.86444478347336</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.974809119889529</v>
+        <v>1.312526002840756</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.2172383726929903</v>
+        <v>2.052690988738493</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6829</v>
+        <v>6799</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>354.0128561656393</v>
+        <v>355.6904821360484</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>211.5</v>
+        <v>81.2</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>44.60434155889664</v>
+        <v>51.09173789719254</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>18.11244445515353</v>
+        <v>11.33819739891984</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.468161479408958</v>
+        <v>1.974809119889529</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-5.079081308711904</v>
+        <v>0.2172383726929903</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6763</v>
+        <v>6829</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>350.9804130864349</v>
+        <v>354.0128561656393</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>41.3</v>
+        <v>211.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>47.07510319617459</v>
+        <v>44.60434155889664</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>16.07849320871835</v>
+        <v>18.11244445515353</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.078066773440332</v>
+        <v>0.468161479408958</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0734770504536445</v>
+        <v>-5.079081308711904</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6720</v>
+        <v>6763</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>348.233328296367</v>
+        <v>350.9804130864349</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>129</v>
+        <v>41.3</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>50.74918504636506</v>
+        <v>47.07510319617459</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>27.23270731342141</v>
+        <v>16.07849320871835</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.2262780857689461</v>
+        <v>1.078066773440332</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.4554392740039379</v>
+        <v>0.0734770504536445</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6754</v>
+        <v>6720</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>344.9100655354231</v>
+        <v>348.233328296367</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>41.8</v>
+        <v>129</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>47.736234407838</v>
+        <v>50.74918504636506</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>12.20639644471981</v>
+        <v>27.23270731342141</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>4.028164558478846</v>
+        <v>0.2262780857689461</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.0599431820699706</v>
+        <v>0.4554392740039379</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6573</v>
+        <v>6754</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>343.958556892678</v>
+        <v>344.9100655354231</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>16.75</v>
+        <v>41.8</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>49.07698722241929</v>
+        <v>47.736234407838</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>16.88127512025667</v>
+        <v>12.20639644471981</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.9936263780951315</v>
+        <v>4.028164558478846</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.025845229357304</v>
+        <v>-0.0599431820699706</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6789</v>
+        <v>6573</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>341.4139537315601</v>
+        <v>343.958556892678</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>433.5</v>
+        <v>16.75</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>43.26629563236376</v>
+        <v>49.07698722241929</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>13.91227733609502</v>
+        <v>16.88127512025667</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.4578195267734292</v>
+        <v>0.9936263780951315</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-3.694642564240708</v>
+        <v>0.025845229357304</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6739</v>
+        <v>6789</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>333.6878960182333</v>
+        <v>341.4139537315601</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>1080</v>
+        <v>433.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>48.27964165741538</v>
+        <v>43.26629563236376</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>14.69586118763659</v>
+        <v>13.91227733609502</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.760819413017897</v>
+        <v>0.4578195267734292</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-9.423960129492158</v>
+        <v>-3.694642564240708</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6526</v>
+        <v>6739</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>330.3974770784726</v>
+        <v>333.6878960182333</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>629</v>
+        <v>1080</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>52.63019806706399</v>
+        <v>48.27964165741538</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>14.79479240110961</v>
+        <v>14.69586118763659</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.7901963113217341</v>
+        <v>0.760819413017897</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.9278431635182764</v>
+        <v>-9.423960129492158</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6674</v>
+        <v>6526</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>328.6716404805138</v>
+        <v>330.3974770784726</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>15.65</v>
+        <v>629</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>46.57036198488466</v>
+        <v>52.63019806706399</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>23.61017770929758</v>
+        <v>14.79479240110961</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.2532677611133509</v>
+        <v>0.7901963113217341</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.0254618573125772</v>
+        <v>-0.9278431635182764</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6658</v>
+        <v>6674</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>324.1227793707258</v>
+        <v>328.6716404805138</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>169</v>
+        <v>15.65</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>50.47813302257954</v>
+        <v>46.57036198488466</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>13.37577884322285</v>
+        <v>23.61017770929758</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.5008344014245039</v>
+        <v>0.2532677611133509</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.925376647091789</v>
+        <v>-0.0254618573125772</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6512</v>
+        <v>6658</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>319.6306004802703</v>
+        <v>324.1227793707258</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>20.55</v>
+        <v>169</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>52.77021245955009</v>
+        <v>50.47813302257954</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>8.133606445424601</v>
+        <v>13.37577884322285</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.737663390414429</v>
+        <v>0.5008344014245039</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.3239655679206402</v>
+        <v>-0.925376647091789</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6488</v>
+        <v>6512</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>307.6994009601287</v>
+        <v>319.6306004802703</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>912</v>
+        <v>20.55</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>45.03688306812226</v>
+        <v>52.77021245955009</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>7.589586143744979</v>
+        <v>8.133606445424601</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.185492404865521</v>
+        <v>0.737663390414429</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-1.678372649270923</v>
+        <v>0.3239655679206402</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6605</v>
+        <v>6488</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>301.4658414921199</v>
+        <v>307.6994009601287</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>136</v>
+        <v>912</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>46.94278006395484</v>
+        <v>45.03688306812226</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>11.4114860462651</v>
+        <v>7.589586143744979</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>3.628726575020433</v>
+        <v>1.185492404865521</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.3176314249188675</v>
+        <v>-1.678372649270923</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6761</v>
+        <v>6605</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>300.2970154148854</v>
+        <v>301.4658414921199</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>39.00836348922889</v>
+        <v>46.94278006395484</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>19.78620218666165</v>
+        <v>11.4114860462651</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.3510678493162599</v>
+        <v>3.628726575020433</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-2.891291605072515</v>
+        <v>-0.3176314249188675</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6669</v>
+        <v>6761</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>300.1939032376561</v>
+        <v>300.2970154148854</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>2135</v>
+        <v>162</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>25.37896830953332</v>
+        <v>39.00836348922889</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>42.37615424059684</v>
+        <v>19.78620218666165</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.419390323765608</v>
+        <v>0.3510678493162599</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-188.4792587058524</v>
+        <v>-2.891291605072515</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6792</v>
+        <v>6669</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>299.2578380823161</v>
+        <v>300.1939032376561</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>59.1</v>
+        <v>2135</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>51.46688298110258</v>
+        <v>25.37896830953332</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>16.39159133809702</v>
+        <v>42.37615424059684</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.6091831486148268</v>
+        <v>1.419390323765608</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.1282048266467608</v>
+        <v>-188.4792587058524</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6794</v>
+        <v>6792</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>298.767231909858</v>
+        <v>299.2578380823161</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>76</v>
+        <v>59.1</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>51.50871166850946</v>
+        <v>51.46688298110258</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>12.98662095879813</v>
+        <v>16.39159133809702</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.7989586199904407</v>
+        <v>0.6091831486148268</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.07500136154173249</v>
+        <v>-0.1282048266467608</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6756</v>
+        <v>6794</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>297.9796445045318</v>
+        <v>298.767231909858</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>95.7</v>
+        <v>76</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>44.41727985327466</v>
+        <v>51.50871166850946</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>10.64091830600402</v>
+        <v>12.98662095879813</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.014906085422984</v>
+        <v>0.7989586199904407</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.7136562673149386</v>
+        <v>0.07500136154173249</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6577</v>
+        <v>6756</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>294.4056869991493</v>
+        <v>297.9796445045318</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>79.3</v>
+        <v>95.7</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,49 +4633,49 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>47.75093810654917</v>
+        <v>44.41727985327466</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>12.38001253675055</v>
+        <v>10.64091830600402</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.3885058835979382</v>
+        <v>1.014906085422984</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0819810156064808</v>
+        <v>-0.7136562673149386</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6585</v>
+        <v>6577</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>290.5838614883457</v>
+        <v>294.4056869991493</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>104.5</v>
+        <v>79.3</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,49 +4686,49 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>36.79454538709151</v>
+        <v>47.75093810654917</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>29.24663527756458</v>
+        <v>12.38001253675055</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.4716541075632446</v>
+        <v>0.3885058835979382</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M80" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.6243468001730497</v>
+        <v>-0.0819810156064808</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6642</v>
+        <v>6585</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>288.5648770070097</v>
+        <v>290.5838614883457</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>75.59999999999999</v>
+        <v>104.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>43.01184083416677</v>
+        <v>36.79454538709151</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>13.07185344902021</v>
+        <v>29.24663527756458</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.3234820539122372</v>
+        <v>0.4716541075632446</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.5645751019019682</v>
+        <v>-0.6243468001730497</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6695</v>
+        <v>6642</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>284.0154223416559</v>
+        <v>288.5648770070097</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>49.55</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>53.44720001865239</v>
+        <v>43.01184083416677</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>10.45000045745602</v>
+        <v>13.07185344902021</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.334833246309472</v>
+        <v>0.3234820539122372</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.1565657087303165</v>
+        <v>-0.5645751019019682</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6831</v>
+        <v>6695</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>278.093573918933</v>
+        <v>284.0154223416559</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>525</v>
+        <v>49.55</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>39.04969407416301</v>
+        <v>53.44720001865239</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>16.71067575473309</v>
+        <v>10.45000045745602</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.3676734661849964</v>
+        <v>1.334833246309472</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-4.720912922752351</v>
+        <v>0.1565657087303165</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6531</v>
+        <v>6831</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>273.9913125026201</v>
+        <v>278.093573918933</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>920</v>
+        <v>525</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>49.82649336687136</v>
+        <v>39.04969407416301</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>11.93221871938665</v>
+        <v>16.71067575473309</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.80151154623694</v>
+        <v>0.3676734661849964</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-4.407785208719176</v>
+        <v>-4.720912922752351</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4926,21 +4926,21 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6645</v>
+        <v>6531</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>263.9176761270658</v>
+        <v>273.9913125026201</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>12.5</v>
+        <v>920</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>43.33763413033677</v>
+        <v>49.82649336687136</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>29.70255097029393</v>
+        <v>11.93221871938665</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.273258649115765</v>
+        <v>0.80151154623694</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0673753917004752</v>
+        <v>-4.407785208719176</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6525</v>
+        <v>6645</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>255.0546499633033</v>
+        <v>263.9176761270658</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>129</v>
+        <v>12.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>42.70726485748469</v>
+        <v>43.33763413033677</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>16.63253926178666</v>
+        <v>29.70255097029393</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.6398028971022702</v>
+        <v>1.273258649115765</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.5165737697222772</v>
+        <v>0.0673753917004752</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6753</v>
+        <v>6525</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>252.9597286335894</v>
+        <v>255.0546499633033</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>43.35404148537916</v>
+        <v>42.70726485748469</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>14.02232346352275</v>
+        <v>16.63253926178666</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.3357378946741427</v>
+        <v>0.6398028971022702</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.7587287733404517</v>
+        <v>-0.5165737697222772</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6835</v>
+        <v>6753</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>252.6247969624287</v>
+        <v>252.9597286335894</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>30.75</v>
+        <v>133</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>45.52370713635912</v>
+        <v>43.35404148537916</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>16.59780382263375</v>
+        <v>14.02232346352275</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.632437720747959</v>
+        <v>0.3357378946741427</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0103804568526427</v>
+        <v>-0.7587287733404517</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6719</v>
+        <v>6835</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>249.8563601504422</v>
+        <v>252.6247969624287</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>181</v>
+        <v>30.75</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>37.14380794525546</v>
+        <v>45.52370713635912</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>26.14859518143198</v>
+        <v>16.59780382263375</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.9044146693084411</v>
+        <v>0.632437720747959</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.4865022632892204</v>
+        <v>0.0103804568526427</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6680</v>
+        <v>6719</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>249.1109357131472</v>
+        <v>249.8563601504422</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>43.14179437514046</v>
+        <v>37.14380794525546</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>7.535878935783493</v>
+        <v>26.14859518143198</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.06377688898497449</v>
+        <v>0.9044146693084411</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-1.092209153993294</v>
+        <v>0.4865022632892204</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6796</v>
+        <v>6680</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>244.0606185117997</v>
+        <v>249.1109357131472</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>50.4</v>
+        <v>0</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>27.38161169877831</v>
+        <v>43.14179437514046</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>25.55878301869088</v>
+        <v>7.535878935783493</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.6060618511799716</v>
+        <v>0.06377688898497449</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-1.076291531301096</v>
+        <v>-1.092209153993294</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6541</v>
+        <v>6796</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>240.7809741314212</v>
+        <v>244.0606185117997</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>30.8</v>
+        <v>50.4</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>29.31942878537789</v>
+        <v>27.38161169877831</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>34.96580635208538</v>
+        <v>25.55878301869088</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.773570876171721</v>
+        <v>0.6060618511799716</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0597940071475477</v>
+        <v>-1.076291531301096</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5350,21 +5350,21 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6692</v>
+        <v>6541</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>240.3739373684737</v>
+        <v>240.7809741314212</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>23.45</v>
+        <v>30.8</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>51.46307330348861</v>
+        <v>29.31942878537789</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>11.29712397153042</v>
+        <v>34.96580635208538</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.961274146390224</v>
+        <v>0.773570876171721</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.4592941195507324</v>
+        <v>-0.0597940071475477</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6725</v>
+        <v>6692</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>237.240679030377</v>
+        <v>240.3739373684737</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>216</v>
+        <v>23.45</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>41.0414628211596</v>
+        <v>51.46307330348861</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>32.46787943267299</v>
+        <v>11.29712397153042</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.740582480901721</v>
+        <v>0.961274146390224</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.6055768288723495</v>
+        <v>-0.4592941195507324</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6558</v>
+        <v>6725</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>234.6934619177773</v>
+        <v>237.240679030377</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>23.8</v>
+        <v>216</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>42.66542321274357</v>
+        <v>41.0414628211596</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>30.29999847613908</v>
+        <v>32.46787943267299</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.7005421153371523</v>
+        <v>1.740582480901721</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.0100780279847796</v>
+        <v>0.6055768288723495</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6757</v>
+        <v>6558</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>233.9571957206388</v>
+        <v>234.6934619177773</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>53.4</v>
+        <v>23.8</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>38.06931830132579</v>
+        <v>42.66542321274357</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>17.004229290436</v>
+        <v>30.29999847613908</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.4943848839933103</v>
+        <v>0.7005421153371523</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.2231058198742685</v>
+        <v>-0.0100780279847796</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6485</v>
+        <v>6757</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>230.731370190744</v>
+        <v>233.9571957206388</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>59.4</v>
+        <v>53.4</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>43.07579658064262</v>
+        <v>38.06931830132579</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>17.26626357881146</v>
+        <v>17.004229290436</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.578553604269292</v>
+        <v>0.4943848839933103</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.1000101897741314</v>
+        <v>-0.2231058198742685</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6614</v>
+        <v>6485</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>229.8143821513201</v>
+        <v>230.731370190744</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>35.65</v>
+        <v>59.4</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>43.54496809079611</v>
+        <v>43.07579658064262</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>9.847608954250539</v>
+        <v>17.26626357881146</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.8268052037401883</v>
+        <v>1.578553604269292</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.0715145766961021</v>
+        <v>0.1000101897741314</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6776</v>
+        <v>6614</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>226.9028636188241</v>
+        <v>229.8143821513201</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>52</v>
+        <v>35.65</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>38.71649490006612</v>
+        <v>43.54496809079611</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>20.39294291101374</v>
+        <v>9.847608954250539</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.9717786454826982</v>
+        <v>0.8268052037401883</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0440364746343839</v>
+        <v>0.0715145766961021</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6494</v>
+        <v>6776</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>223.3714813156748</v>
+        <v>226.9028636188241</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>49.6</v>
+        <v>52</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>35.64132793413937</v>
+        <v>38.71649490006612</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>16.5533767340263</v>
+        <v>20.39294291101374</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.5837084000238659</v>
+        <v>0.9717786454826982</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.5382051948144482</v>
+        <v>-0.0440364746343839</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6788</v>
+        <v>6494</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>221.9346917880705</v>
+        <v>223.3714813156748</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>324.5</v>
+        <v>49.6</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>37.62774511133473</v>
+        <v>35.64132793413937</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>17.89752211845171</v>
+        <v>16.5533767340263</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.7161203936333336</v>
+        <v>0.5837084000238659</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-3.333456950011999</v>
+        <v>-0.5382051948144482</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6517</v>
+        <v>6788</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>220.9880065221331</v>
+        <v>221.9346917880705</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>63.5</v>
+        <v>324.5</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>45.17291975122912</v>
+        <v>37.62774511133473</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>14.43160475383033</v>
+        <v>17.89752211845171</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.2577980039329465</v>
+        <v>0.7161203936333336</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.6850427891316087</v>
+        <v>-3.333456950011999</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6624</v>
+        <v>6517</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>218.4378621879631</v>
+        <v>220.9880065221331</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>38.75</v>
+        <v>63.5</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>52.04164534031643</v>
+        <v>45.17291975122912</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>7.427929366633203</v>
+        <v>14.43160475383033</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.378885336825482</v>
+        <v>0.2577980039329465</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>1.097731571131965</v>
+        <v>-0.6850427891316087</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6781</v>
+        <v>6624</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>216.567589271958</v>
+        <v>218.4378621879631</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>996</v>
+        <v>38.75</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>41.32367116879508</v>
+        <v>52.04164534031643</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>13.17561264349708</v>
+        <v>7.427929366633203</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.4878273070267671</v>
+        <v>1.378885336825482</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-11.92149333491868</v>
+        <v>1.097731571131965</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6698</v>
+        <v>6781</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>215.4432438026665</v>
+        <v>216.567589271958</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>31.65</v>
+        <v>996</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>46.17651517082317</v>
+        <v>41.32367116879508</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>13.26173030482893</v>
+        <v>13.17561264349708</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.9272121384232052</v>
+        <v>0.4878273070267671</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.129009582634489</v>
+        <v>-11.92149333491868</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6671</v>
+        <v>6698</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>211.4303117482014</v>
+        <v>215.4432438026665</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>22.95</v>
+        <v>31.65</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>48.38737280342071</v>
+        <v>46.17651517082317</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>14.16422256113094</v>
+        <v>13.26173030482893</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.1140905650905688</v>
+        <v>0.9272121384232052</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0074039186503703</v>
+        <v>0.129009582634489</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6552</v>
+        <v>6671</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>208.1991132943718</v>
+        <v>211.4303117482014</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>23.95</v>
+        <v>22.95</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>43.78596342702159</v>
+        <v>48.38737280342071</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>16.16810895285896</v>
+        <v>14.16422256113094</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.6038048635302439</v>
+        <v>0.1140905650905688</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0013586553147076</v>
+        <v>0.0074039186503703</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6679</v>
+        <v>6552</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>202.7154351154416</v>
+        <v>208.1991132943718</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>196.5</v>
+        <v>23.95</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>41.798773548258</v>
+        <v>43.78596342702159</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>15.12974180915939</v>
+        <v>16.16810895285896</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.8427182856036699</v>
+        <v>0.6038048635302439</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.3292288435040493</v>
+        <v>0.0013586553147076</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6722</v>
+        <v>6679</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>202.4273666195931</v>
+        <v>202.7154351154416</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>32.4</v>
+        <v>196.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>44.33225766871563</v>
+        <v>41.798773548258</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>17.41410248294262</v>
+        <v>15.12974180915939</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.843862371929881</v>
+        <v>0.8427182856036699</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0014149803537027</v>
+        <v>0.3292288435040493</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6807</v>
+        <v>6722</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>201.4300102717361</v>
+        <v>202.4273666195931</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>32.9</v>
+        <v>32.4</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>50.48467994425097</v>
+        <v>44.33225766871563</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>19.06423670928295</v>
+        <v>17.41410248294262</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.4459656829406977</v>
+        <v>0.843862371929881</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.3038366312208882</v>
+        <v>0.0014149803537027</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6606</v>
+        <v>6807</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>194.8618903674697</v>
+        <v>201.4300102717361</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>25.05</v>
+        <v>32.9</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>41.30107912301446</v>
+        <v>50.48467994425097</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>16.81957467138663</v>
+        <v>19.06423670928295</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.6966824562004449</v>
+        <v>0.4459656829406977</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0870091739949964</v>
+        <v>0.3038366312208882</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6732</v>
+        <v>6606</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>190.8040668526272</v>
+        <v>194.8618903674697</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>150.5</v>
+        <v>25.05</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>48.07271180586196</v>
+        <v>41.30107912301446</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>20.06009473178305</v>
+        <v>16.81957467138663</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.8998305996969148</v>
+        <v>0.6966824562004449</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.6350731705746773</v>
+        <v>-0.0870091739949964</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6534</v>
+        <v>6732</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>182.4239672455996</v>
+        <v>190.8040668526272</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>90.09999999999999</v>
+        <v>150.5</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>38.56595471363158</v>
+        <v>48.07271180586196</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>11.67655910005328</v>
+        <v>20.06009473178305</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.4661477256081023</v>
+        <v>0.8998305996969148</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,51 +6453,51 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.1707635191423718</v>
+        <v>0.6350731705746773</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6550</v>
+        <v>6534</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>168.3885738188338</v>
+        <v>182.4239672455996</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>9.92</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G114" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>35.93313319229829</v>
+        <v>38.56595471363158</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>14.42531059037317</v>
+        <v>11.67655910005328</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.5912643743928939</v>
+        <v>0.4661477256081023</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,48 +6506,48 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0329445662563818</v>
+        <v>-0.1707635191423718</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6546</v>
+        <v>6550</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>160.6427272431833</v>
+        <v>168.3885738188338</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>60.4</v>
+        <v>9.92</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G115" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>45.01824182279395</v>
+        <v>35.93313319229829</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>14.5841755710314</v>
+        <v>14.42531059037317</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.335488092169224</v>
+        <v>0.5912643743928939</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>2</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.2114413595756863</v>
+        <v>-0.0329445662563818</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6569,21 +6569,21 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6591</v>
+        <v>6546</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>157.4637476793502</v>
+        <v>160.6427272431833</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>42.65</v>
+        <v>60.4</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,16 +6594,16 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>46.67698168025131</v>
+        <v>45.01824182279395</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>24.34793722302143</v>
+        <v>14.5841755710314</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.9016901244225252</v>
+        <v>1.335488092169224</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.1388106488804914</v>
+        <v>-0.2114413595756863</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6803</v>
+        <v>6591</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>157.4442470895709</v>
+        <v>157.4637476793502</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>267.5</v>
+        <v>42.65</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>39.83015401169445</v>
+        <v>46.67698168025131</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>14.78199338090966</v>
+        <v>24.34793722302143</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.947432304938013</v>
+        <v>0.9016901244225252</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.08569810597418449</v>
+        <v>0.1388106488804914</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6823</v>
+        <v>6803</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>157.3335951869172</v>
+        <v>157.4442470895709</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>59.4</v>
+        <v>267.5</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>42.18384821183798</v>
+        <v>39.83015401169445</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>27.23212047705949</v>
+        <v>14.78199338090966</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.6154688002517359</v>
+        <v>0.947432304938013</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0238992383603866</v>
+        <v>-0.08569810597418449</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6556</v>
+        <v>6823</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>156.5822613038994</v>
+        <v>157.3335951869172</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>61.4</v>
+        <v>59.4</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>48.889557578306</v>
+        <v>42.18384821183798</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>9.665996580872465</v>
+        <v>27.23212047705949</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.2826433382080019</v>
+        <v>0.6154688002517359</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.2297046719468537</v>
+        <v>-0.0238992383603866</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6561</v>
+        <v>6556</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>153.9672316021551</v>
+        <v>156.5822613038994</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>316.5</v>
+        <v>61.4</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>45.14382776463202</v>
+        <v>48.889557578306</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>14.04010526754424</v>
+        <v>9.665996580872465</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.6470359845820556</v>
+        <v>0.2826433382080019</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.559903905283984</v>
+        <v>0.2297046719468537</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6735</v>
+        <v>6561</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>153.4944459833503</v>
+        <v>153.9672316021551</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>60.5</v>
+        <v>316.5</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>41.79494691995918</v>
+        <v>45.14382776463202</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>14.49107641893075</v>
+        <v>14.04010526754424</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.7331423959205173</v>
+        <v>0.6470359845820556</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>2</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.0847473736847881</v>
+        <v>-0.559903905283984</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6477</v>
+        <v>6735</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>143.7667086749429</v>
+        <v>153.4944459833503</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>33.8</v>
+        <v>60.5</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>41.93228383541695</v>
+        <v>41.79494691995918</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>10.71570396769786</v>
+        <v>14.49107641893075</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.4423158266717353</v>
+        <v>0.7331423959205173</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.1512986748387502</v>
+        <v>0.0847473736847881</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6641</v>
+        <v>6477</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>108.943746813187</v>
+        <v>143.7667086749429</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>17.05</v>
+        <v>33.8</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>51.20370254625074</v>
+        <v>41.93228383541695</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>11.99292434261674</v>
+        <v>10.71570396769786</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.1292684288303851</v>
+        <v>0.4423158266717353</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.0891558224556292</v>
+        <v>-0.1512986748387502</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6592</v>
+        <v>6641</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>93.84326240103792</v>
+        <v>108.943746813187</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>59.8</v>
+        <v>17.05</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>42.50272391984139</v>
+        <v>51.20370254625074</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>10.22139466855934</v>
+        <v>11.99292434261674</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.4155677231477099</v>
+        <v>0.1292684288303851</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.1065259973481373</v>
+        <v>-0.0891558224556292</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7046,21 +7046,21 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6498</v>
+        <v>6592</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>86.69118047446332</v>
+        <v>93.84326240103792</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>65.8</v>
+        <v>59.8</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>37.13342074245274</v>
+        <v>42.50272391984139</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>18.73956664627214</v>
+        <v>10.22139466855934</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.6314194494538096</v>
+        <v>0.4155677231477099</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.6644818340628373</v>
+        <v>-0.1065259973481373</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>6625</v>
+        <v>6498</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>63.37715397667454</v>
+        <v>86.69118047446332</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>74.40000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>41.65395510372839</v>
+        <v>37.13342074245274</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>14.19439717693153</v>
+        <v>18.73956664627214</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.5237615765374897</v>
+        <v>0.6314194494538096</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.2446386044061829</v>
+        <v>-0.6644818340628373</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7152,52 +7152,105 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
+        <v>6625</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>必應</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>63.37715397667454</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>41.65395510372839</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>14.19439717693153</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.5237615765374897</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>-0.2446386044061829</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
         <v>6821</v>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>聯寶</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D127" s="2" t="n">
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
         <v>53.3397232376809</v>
       </c>
-      <c r="E127" s="2" t="n">
+      <c r="E128" s="2" t="n">
         <v>41.4</v>
       </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H127" s="2" t="n">
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
         <v>48.07288632499729</v>
       </c>
-      <c r="I127" s="2" t="n">
+      <c r="I128" s="2" t="n">
         <v>12.4878833053755</v>
       </c>
-      <c r="J127" s="2" t="n">
+      <c r="J128" s="2" t="n">
         <v>0.482544553037316</v>
       </c>
-      <c r="K127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N127" s="2" t="n">
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
         <v>0.1790298499622339</v>
       </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="O128" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
